--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_19_23.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_19_23.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>450573.3717933269</v>
+        <v>457580.9017633517</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11084646.13170057</v>
+        <v>11084131.224384</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17470502.92572541</v>
+        <v>17470866.05278373</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5590187.260740483</v>
+        <v>5590064.553880201</v>
       </c>
     </row>
     <row r="11">
@@ -7959,22 +7959,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>213.9533887334228</v>
+        <v>213.7089309661116</v>
       </c>
       <c r="L2" t="n">
-        <v>228.1535908493842</v>
+        <v>227.8503193726002</v>
       </c>
       <c r="M2" t="n">
-        <v>221.875499558931</v>
+        <v>221.5380516068512</v>
       </c>
       <c r="N2" t="n">
-        <v>220.805264601616</v>
+        <v>220.4623563888806</v>
       </c>
       <c r="O2" t="n">
-        <v>221.9701109191742</v>
+        <v>221.6463124176202</v>
       </c>
       <c r="P2" t="n">
-        <v>224.2958500266263</v>
+        <v>224.0194954968931</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8035,28 +8035,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J3" t="n">
-        <v>124.3990228930818</v>
+        <v>124.3018764260165</v>
       </c>
       <c r="K3" t="n">
-        <v>133.673476710208</v>
+        <v>133.5074379247318</v>
       </c>
       <c r="L3" t="n">
-        <v>132.9500401572327</v>
+        <v>132.7267805197011</v>
       </c>
       <c r="M3" t="n">
-        <v>135.5940339220183</v>
+        <v>135.3335004554958</v>
       </c>
       <c r="N3" t="n">
-        <v>124.6286177437107</v>
+        <v>124.3611887315708</v>
       </c>
       <c r="O3" t="n">
-        <v>136.4550746331237</v>
+        <v>136.210429333514</v>
       </c>
       <c r="P3" t="n">
-        <v>129.045577225651</v>
+        <v>128.8492278044037</v>
       </c>
       <c r="Q3" t="n">
-        <v>136.6869816331913</v>
+        <v>136.5557272449332</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8120,16 +8120,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L4" t="n">
-        <v>131.6674959533694</v>
+        <v>131.5393333932398</v>
       </c>
       <c r="M4" t="n">
-        <v>135.5337183738346</v>
+        <v>135.3985889238948</v>
       </c>
       <c r="N4" t="n">
-        <v>124.3741346291676</v>
+        <v>124.2422182555182</v>
       </c>
       <c r="O4" t="n">
-        <v>135.3979155010231</v>
+        <v>135.2760693786741</v>
       </c>
       <c r="P4" t="n">
         <v>135.0065633140411</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>101.2048693508069</v>
+        <v>101.1996294891914</v>
       </c>
       <c r="K5" t="n">
-        <v>100.4288359696037</v>
+        <v>100.420982775336</v>
       </c>
       <c r="L5" t="n">
-        <v>87.31634461822844</v>
+        <v>87.30660203631251</v>
       </c>
       <c r="M5" t="n">
-        <v>65.16692669460943</v>
+        <v>65.1560861950334</v>
       </c>
       <c r="N5" t="n">
-        <v>61.56098319458087</v>
+        <v>61.54996728438832</v>
       </c>
       <c r="O5" t="n">
-        <v>71.60025162269176</v>
+        <v>71.58984961107134</v>
       </c>
       <c r="P5" t="n">
-        <v>95.95865404672682</v>
+        <v>95.94977617046786</v>
       </c>
       <c r="Q5" t="n">
-        <v>120.7202928895249</v>
+        <v>120.7136259741826</v>
       </c>
       <c r="R5" t="n">
         <v>65.71641987298243</v>
@@ -8272,28 +8272,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J6" t="n">
-        <v>79.28485308176103</v>
+        <v>79.28173225607949</v>
       </c>
       <c r="K6" t="n">
-        <v>56.56617482341559</v>
+        <v>56.56084083524804</v>
       </c>
       <c r="L6" t="n">
-        <v>29.26975713836474</v>
+        <v>29.26258493301845</v>
       </c>
       <c r="M6" t="n">
-        <v>14.60403392201833</v>
+        <v>14.59566429667028</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4363724606917856</v>
+        <v>0.4277813162653672</v>
       </c>
       <c r="O6" t="n">
-        <v>22.84343312368972</v>
+        <v>22.83557390495585</v>
       </c>
       <c r="P6" t="n">
-        <v>37.86221873508495</v>
+        <v>37.85591101917005</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.73332125583283</v>
+        <v>75.72910471478852</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8354,22 +8354,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K7" t="n">
-        <v>79.98834013774851</v>
+        <v>79.98512269717254</v>
       </c>
       <c r="L7" t="n">
-        <v>72.14965988779565</v>
+        <v>72.14554267158444</v>
       </c>
       <c r="M7" t="n">
-        <v>72.78050525908048</v>
+        <v>72.77616423186205</v>
       </c>
       <c r="N7" t="n">
-        <v>63.11305266195447</v>
+        <v>63.10881485466062</v>
       </c>
       <c r="O7" t="n">
-        <v>78.81339091085917</v>
+        <v>78.80947660991431</v>
       </c>
       <c r="P7" t="n">
-        <v>86.69298765570502</v>
+        <v>86.68963829503031</v>
       </c>
       <c r="Q7" t="n">
         <v>65.34295837775146</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>92.3336432201536</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K8" t="n">
-        <v>87.13316762789512</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L8" t="n">
-        <v>70.82189235692189</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M8" t="n">
-        <v>46.8136704132024</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N8" t="n">
-        <v>42.91075203880197</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O8" t="n">
-        <v>53.9893672005812</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P8" t="n">
-        <v>80.92817163466651</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q8" t="n">
-        <v>109.4330265578666</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>74.00121157232707</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K9" t="n">
-        <v>47.53558991775522</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L9" t="n">
-        <v>17.12702128930813</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4340339220183296</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>9.537565199161406</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P9" t="n">
-        <v>27.18308665961325</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q9" t="n">
-        <v>68.59460427470076</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8591,22 +8591,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K10" t="n">
-        <v>74.54112702299442</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L10" t="n">
-        <v>65.17910251074647</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M10" t="n">
-        <v>65.43102984924441</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N10" t="n">
-        <v>55.93833135047905</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O10" t="n">
-        <v>72.18637451741654</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P10" t="n">
-        <v>81.02243027865583</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L11" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M11" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P11" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,10 +8746,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K12" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L13" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M13" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N13" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O13" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P13" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K14" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L14" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M14" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P14" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,10 +8983,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K15" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L16" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M16" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N16" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O16" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P16" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L17" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M17" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P17" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,10 +9220,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K18" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L19" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M19" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N19" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O19" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P19" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K20" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L20" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M20" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P20" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,10 +9457,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K21" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L22" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M22" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N22" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O22" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P22" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K23" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L23" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M23" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P23" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,10 +9694,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K24" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L25" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M25" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N25" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O25" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P25" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K26" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L26" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M26" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P26" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,10 +9931,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K27" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L28" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M28" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N28" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O28" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P28" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K29" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L29" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M29" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P29" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,10 +10168,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K30" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L31" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M31" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N31" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O31" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P31" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K32" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L32" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M32" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P32" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,10 +10405,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K33" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L34" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M34" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N34" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O34" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P34" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K35" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L35" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M35" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P35" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,10 +10642,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K36" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L37" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M37" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N37" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O37" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P37" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K38" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L38" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M38" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P38" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,10 +10879,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K39" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L40" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M40" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N40" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O40" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P40" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K41" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L41" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M41" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P41" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,10 +11116,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K42" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L43" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M43" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N43" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O43" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P43" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K44" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L44" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M44" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P44" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,10 +11353,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K45" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M46" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N46" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O46" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P46" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22519,7 +22519,7 @@
         <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.25449630910492</v>
+        <v>15.25257452796785</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22756,7 +22756,7 @@
         <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>14.36203399754709</v>
+        <v>14.36197226041855</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22993,7 +22993,7 @@
         <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2575113844818</v>
+        <v>14.25430980652213</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S12" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R13" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S15" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R16" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S18" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R19" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S21" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R22" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S24" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R25" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S27" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R28" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S30" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R31" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S33" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R34" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S36" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R37" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S39" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R40" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S42" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R43" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S45" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R46" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1062115.949139656</v>
+        <v>1062009.153505589</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1005634.801630783</v>
+        <v>1005630.845769294</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>999221.5706422112</v>
+        <v>999025.3994866922</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>303937.9592620013</v>
+        <v>303957.4663723199</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>471086.1027622971</v>
+        <v>471086.1907222198</v>
       </c>
       <c r="C2" t="n">
-        <v>471126.950762297</v>
+        <v>471126.9535880053</v>
       </c>
       <c r="D2" t="n">
-        <v>471131.7347622972</v>
+        <v>471131.8812985204</v>
       </c>
       <c r="E2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="F2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="G2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="H2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="I2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="J2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="K2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="L2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="M2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="N2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="O2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="P2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11563.356</v>
+        <v>12024.00450509394</v>
       </c>
       <c r="C3" t="n">
-        <v>202153.644</v>
+        <v>201732.3212511905</v>
       </c>
       <c r="D3" t="n">
-        <v>22266.764</v>
+        <v>22935.65365682307</v>
       </c>
       <c r="E3" t="n">
-        <v>48204.18</v>
+        <v>47420.72226727411</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>443380.415405202</v>
+        <v>440919.0220794785</v>
       </c>
       <c r="C4" t="n">
-        <v>377407.0230083097</v>
+        <v>376402.4651976296</v>
       </c>
       <c r="D4" t="n">
-        <v>369981.1852519083</v>
+        <v>368908.2266409085</v>
       </c>
       <c r="E4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="F4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="G4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="H4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="I4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="J4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="K4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="L4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="M4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="N4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="O4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
       <c r="P4" t="n">
-        <v>22972.50352954441</v>
+        <v>22469.90915247437</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33889.2</v>
+        <v>33899.6213386609</v>
       </c>
       <c r="C5" t="n">
-        <v>38728.8</v>
+        <v>38729.13478501392</v>
       </c>
       <c r="D5" t="n">
-        <v>39295.6</v>
+        <v>39312.96135688073</v>
       </c>
       <c r="E5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="F5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="G5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="H5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="I5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="J5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="K5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="L5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="M5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="N5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="O5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="P5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-17746.86864290484</v>
+        <v>-15756.45720101365</v>
       </c>
       <c r="C6" t="n">
-        <v>-147162.5162460126</v>
+        <v>-145736.9676458286</v>
       </c>
       <c r="D6" t="n">
-        <v>39588.18551038884</v>
+        <v>39975.03964390809</v>
       </c>
       <c r="E6" t="n">
-        <v>59341.05012676412</v>
+        <v>60624.01996119748</v>
       </c>
       <c r="F6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="G6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="H6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="I6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="J6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="K6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="L6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="M6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="N6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="O6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
       <c r="P6" t="n">
-        <v>107545.2301267641</v>
+        <v>108044.7422284716</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>12.47804305783955</v>
       </c>
       <c r="C3" t="n">
-        <v>234</v>
+        <v>234.0153571107304</v>
       </c>
       <c r="D3" t="n">
-        <v>260</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="E3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>12.47804305783955</v>
       </c>
       <c r="C3" t="n">
-        <v>222</v>
+        <v>221.5373140528908</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>26.78103540673445</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>59.02482598057776</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27319,13 +27319,13 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>338.9807518645109</v>
+        <v>338.9610704234411</v>
       </c>
       <c r="I2" t="n">
-        <v>208.6160704749285</v>
+        <v>208.5419810076426</v>
       </c>
       <c r="J2" t="n">
-        <v>7.854877294311009</v>
+        <v>7.691768522530872</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27346,19 +27346,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.781191676856363</v>
+        <v>4.573660934093467</v>
       </c>
       <c r="R2" t="n">
-        <v>146.8387862828582</v>
+        <v>146.7180671985084</v>
       </c>
       <c r="S2" t="n">
-        <v>207.9207731038333</v>
+        <v>207.8769805161729</v>
       </c>
       <c r="T2" t="n">
-        <v>222.8846736847344</v>
+        <v>222.876261087807</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3417936113541</v>
+        <v>251.3416398688631</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -27395,13 +27395,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3177058424559</v>
+        <v>137.3166775988975</v>
       </c>
       <c r="H3" t="n">
-        <v>111.9861612176285</v>
+        <v>111.9762305495779</v>
       </c>
       <c r="I3" t="n">
-        <v>88.50795360613206</v>
+        <v>88.47255136081093</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27428,16 +27428,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>98.55526811490728</v>
+        <v>98.49142681748486</v>
       </c>
       <c r="S3" t="n">
-        <v>171.2037371415737</v>
+        <v>171.1846379684609</v>
       </c>
       <c r="T3" t="n">
-        <v>200.0606909589725</v>
+        <v>200.0565464158579</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9396839677673</v>
+        <v>225.9396163201648</v>
       </c>
       <c r="V3" t="n">
         <v>232.8005871494253</v>
@@ -27474,19 +27474,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9693400141965</v>
+        <v>167.9684779693381</v>
       </c>
       <c r="H4" t="n">
-        <v>162.0347790648166</v>
+        <v>162.0271147023483</v>
       </c>
       <c r="I4" t="n">
-        <v>154.7997208288976</v>
+        <v>154.7737967889741</v>
       </c>
       <c r="J4" t="n">
-        <v>91.82927847732851</v>
+        <v>91.76833190583969</v>
       </c>
       <c r="K4" t="n">
-        <v>19.75539346522712</v>
+        <v>19.65523952622401</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27501,22 +27501,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1042604072376609</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.35004325169439</v>
+        <v>84.27785874996061</v>
       </c>
       <c r="R4" t="n">
-        <v>176.3204077706121</v>
+        <v>176.2816470990699</v>
       </c>
       <c r="S4" t="n">
-        <v>223.6394832828739</v>
+        <v>223.6244601920234</v>
       </c>
       <c r="T4" t="n">
-        <v>227.8531304118881</v>
+        <v>227.8494471293112</v>
       </c>
       <c r="U4" t="n">
-        <v>286.317849028622</v>
+        <v>286.3178020079934</v>
       </c>
       <c r="V4" t="n">
         <v>252.137643323828</v>
@@ -27556,10 +27556,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>329.8408222162697</v>
+        <v>329.8401899509017</v>
       </c>
       <c r="I5" t="n">
-        <v>174.2094172085968</v>
+        <v>174.2070370879479</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27586,16 +27586,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>90.77765060446626</v>
+        <v>90.77377250956408</v>
       </c>
       <c r="S5" t="n">
-        <v>187.5837881792102</v>
+        <v>187.582381344393</v>
       </c>
       <c r="T5" t="n">
-        <v>218.9779199158901</v>
+        <v>218.9776496616099</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2703966264295</v>
+        <v>251.2703916874592</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -27632,13 +27632,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.8401964084937</v>
+        <v>136.8401633762177</v>
       </c>
       <c r="H6" t="n">
-        <v>107.3744253685719</v>
+        <v>107.3741063463283</v>
       </c>
       <c r="I6" t="n">
-        <v>72.06738756839621</v>
+        <v>72.06625027293174</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27665,16 +27665,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>68.90779641679407</v>
+        <v>68.90574551811955</v>
       </c>
       <c r="S6" t="n">
-        <v>162.3342088396869</v>
+        <v>162.3335952796497</v>
       </c>
       <c r="T6" t="n">
-        <v>198.135992845765</v>
+        <v>198.1358597025125</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9082688734277</v>
+        <v>225.9082667002516</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -27711,16 +27711,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.569012145344</v>
+        <v>167.5689844521935</v>
       </c>
       <c r="H7" t="n">
-        <v>158.475500376292</v>
+        <v>158.4752541590085</v>
       </c>
       <c r="I7" t="n">
-        <v>142.7607700092255</v>
+        <v>142.7599372006633</v>
       </c>
       <c r="J7" t="n">
-        <v>63.52609814945966</v>
+        <v>63.5241402437195</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -27741,19 +27741,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.82804325169439</v>
+        <v>50.8257243279741</v>
       </c>
       <c r="R7" t="n">
-        <v>158.3202110493006</v>
+        <v>158.3189658645519</v>
       </c>
       <c r="S7" t="n">
-        <v>216.6628603320542</v>
+        <v>216.6623777159678</v>
       </c>
       <c r="T7" t="n">
-        <v>226.1426386086094</v>
+        <v>226.14252028333</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2960129630483</v>
+        <v>286.2960114525128</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -27793,10 +27793,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>328.7703800052144</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I8" t="n">
-        <v>170.1798091683958</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27823,16 +27823,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>84.21193201150143</v>
+        <v>84.01082088999308</v>
       </c>
       <c r="S8" t="n">
-        <v>185.201979133984</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T8" t="n">
-        <v>218.5203721771967</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U8" t="n">
-        <v>251.2620348173842</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -27869,13 +27869,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.7842718801918</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8343121610248</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I9" t="n">
-        <v>70.141915870283</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -27902,16 +27902,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>65.43557000169972</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S9" t="n">
-        <v>161.2954352547812</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T9" t="n">
-        <v>197.9105777514254</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9045896281446</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -27948,16 +27948,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.5221268994424</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H10" t="n">
-        <v>158.0586479172756</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I10" t="n">
-        <v>141.3508027961107</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J10" t="n">
-        <v>60.21131126421376</v>
+        <v>60.10977774604451</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -27978,19 +27978,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>46.90204325169439</v>
+        <v>46.78178798155719</v>
       </c>
       <c r="R10" t="n">
-        <v>156.2120799017597</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S10" t="n">
-        <v>215.8457783648411</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T10" t="n">
-        <v>225.9423107397569</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2934555859991</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04824120603015072</v>
+        <v>0.05016298716719411</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4940502512562812</v>
+        <v>0.5137316923260268</v>
       </c>
       <c r="I2" t="n">
-        <v>1.859819095477387</v>
+        <v>1.933908562763253</v>
       </c>
       <c r="J2" t="n">
-        <v>4.094412060301508</v>
+        <v>4.257520832081646</v>
       </c>
       <c r="K2" t="n">
-        <v>6.136462311557789</v>
+        <v>6.380920078868973</v>
       </c>
       <c r="L2" t="n">
-        <v>7.612824120603015</v>
+        <v>7.916095597386992</v>
       </c>
       <c r="M2" t="n">
-        <v>8.470733668341708</v>
+        <v>8.80818162042158</v>
       </c>
       <c r="N2" t="n">
-        <v>8.607798994974875</v>
+        <v>8.950707207710371</v>
       </c>
       <c r="O2" t="n">
-        <v>8.128100502512563</v>
+        <v>8.451899004066584</v>
       </c>
       <c r="P2" t="n">
-        <v>6.937145728643216</v>
+        <v>7.213500258376478</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.209507537688442</v>
+        <v>5.417038280451338</v>
       </c>
       <c r="R2" t="n">
-        <v>3.030331658291458</v>
+        <v>3.15105074264126</v>
       </c>
       <c r="S2" t="n">
-        <v>1.099296482412061</v>
+        <v>1.143089070072437</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2111758793969849</v>
+        <v>0.2195884763243924</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003859296482412056</v>
+        <v>0.004013038973375529</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,49 +31038,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02581132075471698</v>
+        <v>0.02683956431308883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2492830188679246</v>
+        <v>0.2592136869185159</v>
       </c>
       <c r="I3" t="n">
-        <v>0.888679245283019</v>
+        <v>0.9240814906041552</v>
       </c>
       <c r="J3" t="n">
-        <v>2.438603773584906</v>
+        <v>2.535750240650205</v>
       </c>
       <c r="K3" t="n">
-        <v>4.167962264150944</v>
+        <v>4.334001049627156</v>
       </c>
       <c r="L3" t="n">
-        <v>5.60433962264151</v>
+        <v>5.827599260173082</v>
       </c>
       <c r="M3" t="n">
-        <v>6.539999999999999</v>
+        <v>6.800533466522552</v>
       </c>
       <c r="N3" t="n">
-        <v>6.713094339622642</v>
+        <v>6.980523351762521</v>
       </c>
       <c r="O3" t="n">
-        <v>6.141169811320754</v>
+        <v>6.385815110930395</v>
       </c>
       <c r="P3" t="n">
-        <v>4.928830188679246</v>
+        <v>5.125179609926587</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.294792452830189</v>
+        <v>3.426046841088322</v>
       </c>
       <c r="R3" t="n">
-        <v>1.60256603773585</v>
+        <v>1.666407335158271</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4794339622641506</v>
+        <v>0.498533135376891</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1040377358490566</v>
+        <v>0.1081822789637221</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001698113207547171</v>
+        <v>0.001765760810071635</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02163934426229508</v>
+        <v>0.02250138912069426</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1923934426229509</v>
+        <v>0.2000578050912637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6507540983606559</v>
+        <v>0.6766781382841512</v>
       </c>
       <c r="J4" t="n">
-        <v>1.529901639344262</v>
+        <v>1.590848210833084</v>
       </c>
       <c r="K4" t="n">
-        <v>2.514098360655737</v>
+        <v>2.614252299658842</v>
       </c>
       <c r="L4" t="n">
-        <v>3.217180327868853</v>
+        <v>3.345342887998491</v>
       </c>
       <c r="M4" t="n">
-        <v>3.392065573770491</v>
+        <v>3.527195023710282</v>
       </c>
       <c r="N4" t="n">
-        <v>3.311409836065576</v>
+        <v>3.44332620971497</v>
       </c>
       <c r="O4" t="n">
-        <v>3.058622950819673</v>
+        <v>3.180469073168677</v>
       </c>
       <c r="P4" t="n">
-        <v>2.617180327868851</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.812</v>
+        <v>1.884184501733771</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9729836065573767</v>
+        <v>1.01174427809958</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3771147540983605</v>
+        <v>0.3921378449488262</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09245901639344259</v>
+        <v>0.09614229897023908</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00118032786885246</v>
+        <v>0.001227348497492416</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.940703517587939</v>
+        <v>0.9407652547165033</v>
       </c>
       <c r="H5" t="n">
-        <v>9.633979899497483</v>
+        <v>9.634612164865391</v>
       </c>
       <c r="I5" t="n">
-        <v>36.26647236180905</v>
+        <v>36.26885248245803</v>
       </c>
       <c r="J5" t="n">
-        <v>79.84103517587941</v>
+        <v>79.84627503749489</v>
       </c>
       <c r="K5" t="n">
-        <v>119.6610150753769</v>
+        <v>119.6688682696445</v>
       </c>
       <c r="L5" t="n">
-        <v>148.4500703517588</v>
+        <v>148.4598129336747</v>
       </c>
       <c r="M5" t="n">
-        <v>165.1793065326633</v>
+        <v>165.1901470322393</v>
       </c>
       <c r="N5" t="n">
-        <v>167.85208040201</v>
+        <v>167.8630963122026</v>
       </c>
       <c r="O5" t="n">
-        <v>158.497959798995</v>
+        <v>158.5083618106154</v>
       </c>
       <c r="P5" t="n">
-        <v>135.2743417085427</v>
+        <v>135.2832195848017</v>
       </c>
       <c r="Q5" t="n">
-        <v>101.5853969849246</v>
+        <v>101.5920639002669</v>
       </c>
       <c r="R5" t="n">
-        <v>59.09146733668342</v>
+        <v>59.09534543158561</v>
       </c>
       <c r="S5" t="n">
-        <v>21.43628140703518</v>
+        <v>21.43768824185234</v>
       </c>
       <c r="T5" t="n">
-        <v>4.117929648241205</v>
+        <v>4.118199902521495</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07525628140703511</v>
+        <v>0.07526122037732025</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5033207547169811</v>
+        <v>0.5033537869928918</v>
       </c>
       <c r="H6" t="n">
-        <v>4.861018867924529</v>
+        <v>4.861337890168192</v>
       </c>
       <c r="I6" t="n">
-        <v>17.32924528301887</v>
+        <v>17.33038257848334</v>
       </c>
       <c r="J6" t="n">
-        <v>47.55277358490567</v>
+        <v>47.55589441058721</v>
       </c>
       <c r="K6" t="n">
-        <v>81.2752641509434</v>
+        <v>81.28059813911095</v>
       </c>
       <c r="L6" t="n">
-        <v>109.2846226415094</v>
+        <v>109.2917948468557</v>
       </c>
       <c r="M6" t="n">
-        <v>127.53</v>
+        <v>127.538369625348</v>
       </c>
       <c r="N6" t="n">
-        <v>130.9053396226415</v>
+        <v>130.9139307670679</v>
       </c>
       <c r="O6" t="n">
-        <v>119.7528113207547</v>
+        <v>119.7606705394886</v>
       </c>
       <c r="P6" t="n">
-        <v>96.11218867924529</v>
+        <v>96.11849639516019</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.24845283018868</v>
+        <v>64.252669371233</v>
       </c>
       <c r="R6" t="n">
-        <v>31.25003773584907</v>
+        <v>31.25208863452359</v>
       </c>
       <c r="S6" t="n">
-        <v>9.348962264150938</v>
+        <v>9.349575824188136</v>
       </c>
       <c r="T6" t="n">
-        <v>2.028735849056603</v>
+        <v>2.028868992309067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03311320754716983</v>
+        <v>0.03311538072321658</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.421967213114754</v>
+        <v>0.4219949062652514</v>
       </c>
       <c r="H7" t="n">
-        <v>3.751672131147543</v>
+        <v>3.751918348431057</v>
       </c>
       <c r="I7" t="n">
-        <v>12.68970491803279</v>
+        <v>12.69053772659502</v>
       </c>
       <c r="J7" t="n">
-        <v>29.83308196721311</v>
+        <v>29.83503987295328</v>
       </c>
       <c r="K7" t="n">
-        <v>49.02491803278687</v>
+        <v>49.02813547336284</v>
       </c>
       <c r="L7" t="n">
-        <v>62.73501639344263</v>
+        <v>62.73913360965385</v>
       </c>
       <c r="M7" t="n">
-        <v>66.14527868852457</v>
+        <v>66.149619715743</v>
       </c>
       <c r="N7" t="n">
-        <v>64.57249180327872</v>
+        <v>64.57672961057257</v>
       </c>
       <c r="O7" t="n">
-        <v>59.64314754098362</v>
+        <v>59.64706184192848</v>
       </c>
       <c r="P7" t="n">
-        <v>51.0350163934426</v>
+        <v>51.0383657541173</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.334</v>
+        <v>35.33631892372028</v>
       </c>
       <c r="R7" t="n">
-        <v>18.97318032786885</v>
+        <v>18.97442551261758</v>
       </c>
       <c r="S7" t="n">
-        <v>7.353737704918029</v>
+        <v>7.354220321004425</v>
       </c>
       <c r="T7" t="n">
-        <v>1.80295081967213</v>
+        <v>1.803069144951528</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02301639344262298</v>
+        <v>0.02301790397810465</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.045226130653266</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H8" t="n">
-        <v>10.70442211055276</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I8" t="n">
-        <v>40.29608040201006</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J8" t="n">
-        <v>88.71226130653268</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K8" t="n">
-        <v>132.9566834170854</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L8" t="n">
-        <v>164.9445226130653</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M8" t="n">
-        <v>183.5325628140703</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N8" t="n">
-        <v>186.5023115577889</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O8" t="n">
-        <v>176.1088442211055</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P8" t="n">
-        <v>150.304824120603</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.8726633165829</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R8" t="n">
-        <v>65.65718592964825</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S8" t="n">
-        <v>23.81809045226131</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T8" t="n">
-        <v>4.575477386934672</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08361809045226122</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5592452830188679</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H9" t="n">
-        <v>5.401132075471699</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I9" t="n">
-        <v>19.25471698113208</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J9" t="n">
-        <v>52.83641509433964</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K9" t="n">
-        <v>90.30584905660378</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L9" t="n">
-        <v>121.427358490566</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M9" t="n">
-        <v>141.7</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>133.058679245283</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P9" t="n">
-        <v>106.791320754717</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q9" t="n">
-        <v>71.38716981132076</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R9" t="n">
-        <v>34.72226415094341</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S9" t="n">
-        <v>10.3877358490566</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T9" t="n">
-        <v>2.254150943396226</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679245283018869</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4688524590163934</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H10" t="n">
-        <v>4.168524590163937</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I10" t="n">
-        <v>14.09967213114754</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J10" t="n">
-        <v>33.14786885245901</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K10" t="n">
-        <v>54.47213114754096</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L10" t="n">
-        <v>69.70557377049181</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M10" t="n">
-        <v>73.49475409836064</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N10" t="n">
-        <v>71.74721311475415</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O10" t="n">
-        <v>66.27016393442625</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P10" t="n">
-        <v>56.70557377049177</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.26</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R10" t="n">
-        <v>21.08131147540983</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S10" t="n">
-        <v>8.170819672131143</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T10" t="n">
-        <v>2.003278688524589</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02557377049180331</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J11" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K11" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M11" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S11" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T11" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H12" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I12" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K12" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R12" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S12" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H13" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I13" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K13" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L13" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M13" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N13" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O13" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P13" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R13" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J14" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K14" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M14" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S14" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T14" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H15" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I15" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K15" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R15" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S15" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H16" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I16" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K16" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L16" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M16" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N16" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O16" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P16" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R16" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J17" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K17" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M17" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S17" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T17" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H18" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I18" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K18" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R18" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S18" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H19" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I19" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K19" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L19" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M19" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N19" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O19" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P19" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R19" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J20" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K20" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M20" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S20" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T20" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H21" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I21" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K21" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R21" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S21" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H22" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I22" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K22" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L22" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M22" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N22" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O22" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P22" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R22" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J23" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K23" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M23" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S23" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T23" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H24" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I24" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K24" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R24" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S24" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H25" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I25" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L25" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M25" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N25" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O25" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P25" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R25" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J26" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K26" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M26" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S26" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T26" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H27" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I27" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K27" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R27" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S27" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H28" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I28" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L28" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M28" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N28" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O28" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P28" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R28" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K29" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M29" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S29" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T29" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H30" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I30" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K30" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R30" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S30" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H31" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I31" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K31" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L31" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M31" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N31" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O31" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R31" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J32" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K32" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M32" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S32" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T32" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H33" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I33" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K33" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R33" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S33" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H34" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I34" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K34" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L34" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M34" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N34" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O34" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P34" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R34" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J35" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K35" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M35" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S35" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T35" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H36" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I36" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K36" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R36" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S36" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H37" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I37" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K37" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L37" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M37" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N37" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O37" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P37" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R37" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J38" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K38" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M38" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S38" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T38" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H39" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I39" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K39" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R39" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S39" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H40" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I40" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K40" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L40" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M40" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N40" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O40" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P40" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R40" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J41" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K41" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M41" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S41" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T41" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,19 +34119,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H42" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I42" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K42" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R42" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S42" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I43" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K43" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L43" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M43" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N43" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O43" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P43" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R43" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J44" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K44" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M44" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S44" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T44" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,19 +34356,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H45" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I45" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K45" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R45" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S45" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H46" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I46" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K46" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L46" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M46" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N46" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O46" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P46" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R46" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
